--- a/final_data_pipeline/output/322130_finishing_elec.xlsx
+++ b/final_data_pipeline/output/322130_finishing_elec.xlsx
@@ -1292,7 +1292,7 @@
         <v>70</v>
       </c>
       <c r="K12">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="L12">
         <v>8000</v>
@@ -1313,10 +1313,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R12">
-        <v>1.800714285714286</v>
+        <v>1.867772014163364</v>
       </c>
       <c r="S12">
-        <v>1.963947368421052</v>
+        <v>2.045100507661769</v>
       </c>
       <c r="T12">
         <v>59.56173227185896</v>
@@ -1351,7 +1351,7 @@
         <v>82</v>
       </c>
       <c r="K13">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="L13">
         <v>8000</v>
@@ -1366,10 +1366,10 @@
         <v>295756.2806761013</v>
       </c>
       <c r="R13">
-        <v>2.983181818181818</v>
+        <v>3.202698560003336</v>
       </c>
       <c r="S13">
-        <v>3.590555555555556</v>
+        <v>3.918847414586112</v>
       </c>
       <c r="T13">
         <v>36.96953508451266</v>
@@ -2037,7 +2037,7 @@
         <v>82</v>
       </c>
       <c r="K26">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="L26">
         <v>8000</v>
@@ -2052,10 +2052,10 @@
         <v>286563.8113041536</v>
       </c>
       <c r="R26">
-        <v>2.983181818181818</v>
+        <v>3.745925377867032</v>
       </c>
       <c r="S26">
-        <v>3.590555555555556</v>
+        <v>4.780194493904943</v>
       </c>
       <c r="T26">
         <v>35.82047641301921</v>
@@ -2096,7 +2096,7 @@
         <v>70</v>
       </c>
       <c r="K27">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="L27">
         <v>8000</v>
@@ -2117,10 +2117,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R27">
-        <v>1.800714285714286</v>
+        <v>2.015705049109126</v>
       </c>
       <c r="S27">
-        <v>1.963947368421052</v>
+        <v>2.22640738080769</v>
       </c>
       <c r="T27">
         <v>57.71048029371813</v>
@@ -2161,7 +2161,7 @@
         <v>70</v>
       </c>
       <c r="K28">
-        <v>10</v>
+        <v>2.356481481481501</v>
       </c>
       <c r="L28">
         <v>8000</v>
@@ -2182,10 +2182,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R28">
-        <v>1.800714285714286</v>
+        <v>1.678525338046114</v>
       </c>
       <c r="S28">
-        <v>1.963947368421052</v>
+        <v>1.817698795724144</v>
       </c>
       <c r="T28">
         <v>107.0795230692132</v>
@@ -2220,7 +2220,7 @@
         <v>82</v>
       </c>
       <c r="K29">
-        <v>10</v>
+        <v>2.356481481481501</v>
       </c>
       <c r="L29">
         <v>8000</v>
@@ -2235,10 +2235,10 @@
         <v>531707.8646230728</v>
       </c>
       <c r="R29">
-        <v>2.983181818181818</v>
+        <v>2.619185573867416</v>
       </c>
       <c r="S29">
-        <v>3.590555555555556</v>
+        <v>3.069228739776626</v>
       </c>
       <c r="T29">
         <v>66.46348307788409</v>
@@ -2603,7 +2603,7 @@
         <v>82</v>
       </c>
       <c r="K36">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="L36">
         <v>8000</v>
@@ -2618,10 +2618,10 @@
         <v>173455.9440940882</v>
       </c>
       <c r="R36">
-        <v>2.983181818181818</v>
+        <v>3.702873262981926</v>
       </c>
       <c r="S36">
-        <v>3.590555555555556</v>
+        <v>4.709243017136692</v>
       </c>
       <c r="T36">
         <v>21.68199301176102</v>
@@ -2662,7 +2662,7 @@
         <v>70</v>
       </c>
       <c r="K37">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="L37">
         <v>8000</v>
@@ -2683,10 +2683,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R37">
-        <v>1.800714285714286</v>
+        <v>2.004820578273036</v>
       </c>
       <c r="S37">
-        <v>1.963947368421052</v>
+        <v>2.212959200483225</v>
       </c>
       <c r="T37">
         <v>34.9319259745798</v>
@@ -2727,7 +2727,7 @@
         <v>70</v>
       </c>
       <c r="K38">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="L38">
         <v>8000</v>
@@ -2748,10 +2748,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R38">
-        <v>1.800714285714286</v>
+        <v>2.017497406510892</v>
       </c>
       <c r="S38">
-        <v>1.963947368421052</v>
+        <v>2.228623569098047</v>
       </c>
       <c r="T38">
         <v>75.31909748715492</v>
@@ -2786,7 +2786,7 @@
         <v>82</v>
       </c>
       <c r="K39">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="L39">
         <v>8000</v>
@@ -2801,10 +2801,10 @@
         <v>374000.138797279</v>
       </c>
       <c r="R39">
-        <v>2.983181818181818</v>
+        <v>3.753065762999045</v>
       </c>
       <c r="S39">
-        <v>3.590555555555556</v>
+        <v>4.792008787587529</v>
       </c>
       <c r="T39">
         <v>46.75001734965987</v>
@@ -2839,7 +2839,7 @@
         <v>82</v>
       </c>
       <c r="K40">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="L40">
         <v>8000</v>
@@ -2854,10 +2854,10 @@
         <v>89904.03482076045</v>
       </c>
       <c r="R40">
-        <v>2.983181818181818</v>
+        <v>3.33095021773865</v>
       </c>
       <c r="S40">
-        <v>3.590555555555556</v>
+        <v>4.115751405322535</v>
       </c>
       <c r="T40">
         <v>11.23800435259506</v>
@@ -2898,7 +2898,7 @@
         <v>70</v>
       </c>
       <c r="K41">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="L41">
         <v>8000</v>
@@ -2919,10 +2919,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R41">
-        <v>1.800714285714286</v>
+        <v>1.904889690449167</v>
       </c>
       <c r="S41">
-        <v>1.963947368421052</v>
+        <v>2.090295475371289</v>
       </c>
       <c r="T41">
         <v>18.10558355654463</v>
@@ -2957,7 +2957,7 @@
         <v>82</v>
       </c>
       <c r="K42">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="L42">
         <v>8000</v>
@@ -2972,10 +2972,10 @@
         <v>409239.9259745825</v>
       </c>
       <c r="R42">
-        <v>2.983181818181818</v>
+        <v>2.455497817501559</v>
       </c>
       <c r="S42">
-        <v>3.590555555555556</v>
+        <v>2.843656807626497</v>
       </c>
       <c r="T42">
         <v>51.15499074682281</v>
@@ -3016,7 +3016,7 @@
         <v>70</v>
       </c>
       <c r="K43">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="L43">
         <v>8000</v>
@@ -3037,10 +3037,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R43">
-        <v>1.800714285714286</v>
+        <v>1.618523362263702</v>
       </c>
       <c r="S43">
-        <v>1.963947368421052</v>
+        <v>1.746638928617865</v>
       </c>
       <c r="T43">
         <v>82.41596374600033</v>
@@ -3199,7 +3199,7 @@
         <v>70</v>
       </c>
       <c r="K46">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="L46">
         <v>8000</v>
@@ -3220,10 +3220,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R46">
-        <v>1.800714285714286</v>
+        <v>1.862155209238257</v>
       </c>
       <c r="S46">
-        <v>1.963947368421052</v>
+        <v>2.038278558917324</v>
       </c>
       <c r="T46">
         <v>8.652535208826771</v>
@@ -3258,7 +3258,7 @@
         <v>82</v>
       </c>
       <c r="K47">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="L47">
         <v>8000</v>
@@ -3273,10 +3273,10 @@
         <v>42964.52662090698</v>
       </c>
       <c r="R47">
-        <v>2.983181818181818</v>
+        <v>3.183723085360894</v>
       </c>
       <c r="S47">
-        <v>3.590555555555556</v>
+        <v>3.890038835634921</v>
       </c>
       <c r="T47">
         <v>5.370565827613373</v>
@@ -3665,7 +3665,7 @@
         <v>82</v>
       </c>
       <c r="K54">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="L54">
         <v>8000</v>
@@ -3680,10 +3680,10 @@
         <v>965791.3122671177</v>
       </c>
       <c r="R54">
-        <v>2.983181818181818</v>
+        <v>3.629680458828347</v>
       </c>
       <c r="S54">
-        <v>3.590555555555556</v>
+        <v>4.589715938979482</v>
       </c>
       <c r="T54">
         <v>120.7239140333897</v>
@@ -3718,7 +3718,7 @@
         <v>83</v>
       </c>
       <c r="K55">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="L55">
         <v>8000</v>
@@ -3771,7 +3771,7 @@
         <v>70</v>
       </c>
       <c r="K56">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="L56">
         <v>8000</v>
@@ -3792,10 +3792,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R56">
-        <v>1.800714285714286</v>
+        <v>1.98600466835246</v>
       </c>
       <c r="S56">
-        <v>1.963947368421052</v>
+        <v>2.18975222777657</v>
       </c>
       <c r="T56">
         <v>194.498671136385</v>
@@ -3954,7 +3954,7 @@
         <v>70</v>
       </c>
       <c r="K59">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="L59">
         <v>8000</v>
@@ -3975,10 +3975,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R59">
-        <v>1.800714285714286</v>
+        <v>2.028520339740724</v>
       </c>
       <c r="S59">
-        <v>1.963947368421052</v>
+        <v>2.242263395092639</v>
       </c>
       <c r="T59">
         <v>25.04487808552879</v>
@@ -4013,7 +4013,7 @@
         <v>82</v>
       </c>
       <c r="K60">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="L60">
         <v>8000</v>
@@ -4028,10 +4028,10 @@
         <v>124361.3929620722</v>
       </c>
       <c r="R60">
-        <v>2.983181818181818</v>
+        <v>3.797299903567984</v>
       </c>
       <c r="S60">
-        <v>3.590555555555556</v>
+        <v>4.865495608531995</v>
       </c>
       <c r="T60">
         <v>15.54517412025903</v>
@@ -4072,7 +4072,7 @@
         <v>70</v>
       </c>
       <c r="K61">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="L61">
         <v>8000</v>
@@ -4093,10 +4093,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R61">
-        <v>1.800714285714286</v>
+        <v>1.844936767548521</v>
       </c>
       <c r="S61">
-        <v>1.963947368421052</v>
+        <v>2.017393709936214</v>
       </c>
       <c r="T61">
         <v>142.5753281290024</v>
@@ -4131,7 +4131,7 @@
         <v>82</v>
       </c>
       <c r="K62">
-        <v>10</v>
+        <v>12.51681286549706</v>
       </c>
       <c r="L62">
         <v>8000</v>
@@ -4146,10 +4146,10 @@
         <v>707963.7739739026</v>
       </c>
       <c r="R62">
-        <v>2.983181818181818</v>
+        <v>3.126239257907711</v>
       </c>
       <c r="S62">
-        <v>3.590555555555556</v>
+        <v>3.803269267167952</v>
       </c>
       <c r="T62">
         <v>88.49547174673782</v>
@@ -4190,7 +4190,7 @@
         <v>70</v>
       </c>
       <c r="K63">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="L63">
         <v>8000</v>
@@ -4211,10 +4211,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R63">
-        <v>1.800714285714286</v>
+        <v>1.904889690449167</v>
       </c>
       <c r="S63">
-        <v>1.963947368421052</v>
+        <v>2.090295475371289</v>
       </c>
       <c r="T63">
         <v>182.1474834198667</v>
@@ -4249,7 +4249,7 @@
         <v>82</v>
       </c>
       <c r="K64">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="L64">
         <v>8000</v>
@@ -4264,10 +4264,10 @@
         <v>904460.9714318883</v>
       </c>
       <c r="R64">
-        <v>2.983181818181818</v>
+        <v>3.33095021773865</v>
       </c>
       <c r="S64">
-        <v>3.590555555555556</v>
+        <v>4.115751405322535</v>
       </c>
       <c r="T64">
         <v>113.057621428986</v>
@@ -4302,7 +4302,7 @@
         <v>83</v>
       </c>
       <c r="K65">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="L65">
         <v>8000</v>
@@ -4638,7 +4638,7 @@
         <v>70</v>
       </c>
       <c r="K71">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="L71">
         <v>8000</v>
@@ -4659,10 +4659,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R71">
-        <v>1.800714285714286</v>
+        <v>1.867546171126113</v>
       </c>
       <c r="S71">
-        <v>1.963947368421052</v>
+        <v>2.044826120875009</v>
       </c>
       <c r="T71">
         <v>56.45993263152648</v>
@@ -4697,7 +4697,7 @@
         <v>82</v>
       </c>
       <c r="K72">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="L72">
         <v>8000</v>
@@ -4712,10 +4712,10 @@
         <v>280354.1644172927</v>
       </c>
       <c r="R72">
-        <v>2.983181818181818</v>
+        <v>3.201933436480062</v>
       </c>
       <c r="S72">
-        <v>3.590555555555556</v>
+        <v>3.917684201664166</v>
       </c>
       <c r="T72">
         <v>35.04427055216158</v>
@@ -4750,7 +4750,7 @@
         <v>84</v>
       </c>
       <c r="K73">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="L73">
         <v>8000</v>
@@ -4803,7 +4803,7 @@
         <v>70</v>
       </c>
       <c r="K74">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="L74">
         <v>8000</v>
@@ -4824,10 +4824,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R74">
-        <v>1.800714285714286</v>
+        <v>1.890159325210871</v>
       </c>
       <c r="S74">
-        <v>1.963947368421052</v>
+        <v>2.072335994446373</v>
       </c>
       <c r="T74">
         <v>71.41353200616254</v>
@@ -4862,7 +4862,7 @@
         <v>82</v>
       </c>
       <c r="K75">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="L75">
         <v>8000</v>
@@ -4877,10 +4877,10 @@
         <v>354606.8895324147</v>
       </c>
       <c r="R75">
-        <v>2.983181818181818</v>
+        <v>3.27945034353529</v>
       </c>
       <c r="S75">
-        <v>3.590555555555556</v>
+        <v>4.036221701795472</v>
       </c>
       <c r="T75">
         <v>44.32586119155184</v>
@@ -5876,7 +5876,7 @@
         <v>82</v>
       </c>
       <c r="K93">
-        <v>10</v>
+        <v>19.48611111111111</v>
       </c>
       <c r="L93">
         <v>8000</v>
@@ -5891,10 +5891,10 @@
         <v>152629.8325099519</v>
       </c>
       <c r="R93">
-        <v>2.983181818181818</v>
+        <v>3.604943545926152</v>
       </c>
       <c r="S93">
-        <v>3.590555555555556</v>
+        <v>4.549628470864294</v>
       </c>
       <c r="T93">
         <v>19.07872906374399</v>
@@ -5935,7 +5935,7 @@
         <v>70</v>
       </c>
       <c r="K94">
-        <v>10</v>
+        <v>19.48611111111111</v>
       </c>
       <c r="L94">
         <v>8000</v>
@@ -5956,10 +5956,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R94">
-        <v>1.800714285714286</v>
+        <v>1.979555038534245</v>
       </c>
       <c r="S94">
-        <v>1.963947368421052</v>
+        <v>2.181809322722105</v>
       </c>
       <c r="T94">
         <v>30.73779937952481</v>
@@ -6000,7 +6000,7 @@
         <v>70</v>
       </c>
       <c r="K95">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="L95">
         <v>8000</v>
@@ -6021,10 +6021,10 @@
         <v>5.330714285714286</v>
       </c>
       <c r="R95">
-        <v>1.800714285714286</v>
+        <v>1.880917929007461</v>
       </c>
       <c r="S95">
-        <v>1.963947368421052</v>
+        <v>2.06108460959076</v>
       </c>
       <c r="T95">
         <v>8.542175684527461</v>
@@ -6059,7 +6059,7 @@
         <v>82</v>
       </c>
       <c r="K96">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="L96">
         <v>8000</v>
@@ -6074,10 +6074,10 @@
         <v>42416.53177255418</v>
       </c>
       <c r="R96">
-        <v>2.983181818181818</v>
+        <v>3.247548358074673</v>
       </c>
       <c r="S96">
-        <v>3.590555555555556</v>
+        <v>3.987268648345484</v>
       </c>
       <c r="T96">
         <v>5.302066471569272</v>
